--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-procedure.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Procedure|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,7 +364,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -500,7 +500,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -538,7 +538,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -565,7 +565,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -640,7 +640,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -658,7 +658,7 @@
     <t>検索、並べ替え、表示のプロシジャー（処置等）を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -686,7 +686,7 @@
     <t>0..1主に叙述(Narative)のみのリソースを説明する。 / 0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesMedical_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesMedical_VS|1.1.0a</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -934,7 +934,7 @@
     <t>STEM7 外保連手術基幹コード ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesSTEM7_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesSTEM7_VS|1.1.0a</t>
   </si>
   <si>
     <t>Procedure.code.coding:stem7.id</t>
@@ -970,7 +970,7 @@
     <t>歯科診療行為マスタ ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesDental_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesDental_VS|1.1.0</t>
   </si>
   <si>
     <t>Procedure.code.coding:dental.id</t>
@@ -1006,7 +1006,7 @@
     <t>看護行為マスタ ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesNurse_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesNurse_VS|1.1.0a</t>
   </si>
   <si>
     <t>Procedure.code.coding:nurse.id</t>
@@ -1042,7 +1042,7 @@
     <t>WHO ICHI (International Classification of Health Interventions) ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS|1.1.0</t>
   </si>
   <si>
     <t>Procedure.code.coding:ichi.id</t>
@@ -1100,7 +1100,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1128,7 +1128,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1279,7 +1279,7 @@
     <t>さまざまなパフォーマーの関与の種類の曖昧性を乱すことができます。 / Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1294,7 +1294,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1325,7 +1325,7 @@
     <t>Procedure.performer.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1384,7 +1384,7 @@
 もしプロシージャの異なる理由を説明しているのであれば、Procedure.reasonCodeとProcedure.reasonReferenceの両方を使用できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1399,7 +1399,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1431,7 +1431,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張extension [procedure-targetbodystructure]（extension-procedure-targetbodystructure.html）を使用する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS|1.1.0</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1452,7 +1452,7 @@
     <t>結果に叙述的記述トのみが含まれている場合は、CodeableConcept.textを使用してその情報を格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS|1.1.0</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUT].target.text</t>
@@ -1461,7 +1461,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference|Composition)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1|Composition|4.0.1)
 </t>
   </si>
   <si>
@@ -1490,7 +1490,7 @@
     <t>合併症が叙述的なテキストによってのみ表現されている場合は、CodeableConcept.textに格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS|1.1.0</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
@@ -1499,7 +1499,7 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1521,7 +1521,7 @@
     <t>プロシジャー（処置等）で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|1.1.0</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
@@ -1583,7 +1583,7 @@
     <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|1.1.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
@@ -1592,7 +1592,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1608,7 +1608,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|Substance)
+    <t xml:space="preserve">Reference(Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev|Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1637,7 +1637,7 @@
     <t>Procedureの一部として使用されたコード化されたアイテムを識別する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS|1.1.0</t>
   </si>
   <si>
     <t>participation[typeCode=Dev].role[classCode=MANU]</t>
@@ -1957,7 +1957,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="227.4375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1972,7 +1972,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="59.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.7421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.26953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-procedure.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Procedure|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,7 +364,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -500,7 +500,7 @@
     <t>Procedure.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
 </t>
   </si>
   <si>
@@ -538,7 +538,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -565,7 +565,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration)
 </t>
   </si>
   <si>
@@ -640,7 +640,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureNotPerformedReason_VS</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -658,7 +658,7 @@
     <t>検索、並べ替え、表示のプロシジャー（処置等）を分類するコード（「外科的処置」など）。 / A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCategory_VS</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -686,7 +686,7 @@
     <t>0..1主に叙述(Narative)のみのリソースを説明する。 / 0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesMedical_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesMedical_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -934,7 +934,7 @@
     <t>STEM7 外保連手術基幹コード ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesSTEM7_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesSTEM7_VS</t>
   </si>
   <si>
     <t>Procedure.code.coding:stem7.id</t>
@@ -970,7 +970,7 @@
     <t>歯科診療行為マスタ ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesDental_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesDental_VS</t>
   </si>
   <si>
     <t>Procedure.code.coding:dental.id</t>
@@ -1006,7 +1006,7 @@
     <t>看護行為マスタ ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesNurse_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesNurse_VS</t>
   </si>
   <si>
     <t>Procedure.code.coding:nurse.id</t>
@@ -1042,7 +1042,7 @@
     <t>WHO ICHI (International Classification of Health Interventions) ValueSet</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCodesICHI_VS</t>
   </si>
   <si>
     <t>Procedure.code.coding:ichi.id</t>
@@ -1100,7 +1100,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1128,7 +1128,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -1279,7 +1279,7 @@
     <t>さまざまなパフォーマーの関与の種類の曖昧性を乱すことができます。 / Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedurePerformerRole_VS</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1294,7 +1294,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
@@ -1325,7 +1325,7 @@
     <t>Procedure.performer.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>Procedure.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -1384,7 +1384,7 @@
 もしプロシージャの異なる理由を説明しているのであれば、Procedure.reasonCodeとProcedure.reasonReferenceの両方を使用できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureReason_VS</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1399,7 +1399,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference)
 </t>
   </si>
   <si>
@@ -1431,7 +1431,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張extension [procedure-targetbodystructure]（extension-procedure-targetbodystructure.html）を使用する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureBodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1452,7 +1452,7 @@
     <t>結果に叙述的記述トのみが含まれている場合は、CodeableConcept.textを使用してその情報を格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureOutcome_VS</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUT].target.text</t>
@@ -1461,7 +1461,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1|Composition|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference|Composition)
 </t>
   </si>
   <si>
@@ -1490,7 +1490,7 @@
     <t>合併症が叙述的なテキストによってのみ表現されている場合は、CodeableConcept.textに格納できる。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureCondition_VS</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=OUTC].target[classCode=OBS, code="complication", moodCode=EVN].value</t>
@@ -1499,7 +1499,7 @@
     <t>Procedure.complicationDetail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition)
 </t>
   </si>
   <si>
@@ -1521,7 +1521,7 @@
     <t>プロシジャー（処置等）で特定のフォローアップが必要な場合 - 例えば縫合の除去。フォローアップは、単純なメモとして表されるか、潜在的により複雑になる可能性があります。その場合、カレプランリソースを使用できます。 / If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureFollowUp_VS</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=ACT, moodCode=INT].code</t>
@@ -1583,7 +1583,7 @@
     <t>Procedure中にデバイスに起こった変化の種類。【JP Core仕様】https://www.hl7.org/fhir/R4/procedure.htmlを参照</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceAction_VS</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="procedure device action"].value=:procedure device action codes</t>
@@ -1592,7 +1592,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(Device)
 </t>
   </si>
   <si>
@@ -1608,7 +1608,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev|Substance|4.0.1)
+    <t xml:space="preserve">Reference(Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|Substance)
 </t>
   </si>
   <si>
@@ -1637,7 +1637,7 @@
     <t>Procedureの一部として使用されたコード化されたアイテムを識別する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ProcedureDeviceKind_VS</t>
   </si>
   <si>
     <t>participation[typeCode=Dev].role[classCode=MANU]</t>
@@ -1957,7 +1957,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="227.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1972,7 +1972,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="59.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.26953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
